--- a/documents/grille_E5.xlsx
+++ b/documents/grille_E5.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\z-bla\Documents\DOC PORTFOLIO\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\z-bla\Documents\protfolio_blann\documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4C8E8B52-CE68-472F-B4E8-9D602BF4C1A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{02E1EFD0-7AC1-47FA-A313-6E8E25C2624E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -122,9 +122,6 @@
     <t>☐ SLAM</t>
   </si>
   <si>
-    <t>Adresse URL du portfolio : À compléter</t>
-  </si>
-  <si>
     <t>Installation et paramétrage de WampServer</t>
   </si>
   <si>
@@ -213,6 +210,9 @@
   </si>
   <si>
     <t>01 au  03 Juillet 2026</t>
+  </si>
+  <si>
+    <t>Adresse URL du portfolio : https://blann973.github.io/portfolio-blann/</t>
   </si>
 </sst>
 </file>
@@ -909,9 +909,60 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="15" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -935,57 +986,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="15" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1232,58 +1232,58 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="31.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="36" t="s">
+      <c r="A1" s="39" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="36"/>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
-      <c r="E1" s="36"/>
-      <c r="F1" s="36"/>
-      <c r="G1" s="36" t="s">
+      <c r="B1" s="39"/>
+      <c r="C1" s="39"/>
+      <c r="D1" s="39"/>
+      <c r="E1" s="39"/>
+      <c r="F1" s="39"/>
+      <c r="G1" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="36"/>
+      <c r="H1" s="39"/>
     </row>
     <row r="2" spans="1:43" ht="32.85" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="36" t="s">
+      <c r="A2" s="39" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="36"/>
-      <c r="C2" s="36"/>
-      <c r="D2" s="36"/>
-      <c r="E2" s="36"/>
-      <c r="F2" s="36"/>
-      <c r="G2" s="36"/>
-      <c r="H2" s="36"/>
+      <c r="B2" s="39"/>
+      <c r="C2" s="39"/>
+      <c r="D2" s="39"/>
+      <c r="E2" s="39"/>
+      <c r="F2" s="39"/>
+      <c r="G2" s="39"/>
+      <c r="H2" s="39"/>
     </row>
     <row r="3" spans="1:43" ht="31.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="37" t="s">
+      <c r="A3" s="54" t="s">
         <v>22</v>
       </c>
-      <c r="B3" s="38"/>
-      <c r="C3" s="38"/>
-      <c r="D3" s="38"/>
-      <c r="E3" s="39"/>
-      <c r="F3" s="43" t="s">
+      <c r="B3" s="55"/>
+      <c r="C3" s="55"/>
+      <c r="D3" s="55"/>
+      <c r="E3" s="56"/>
+      <c r="F3" s="60" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="38" t="s">
+      <c r="G3" s="55" t="s">
         <v>23</v>
       </c>
-      <c r="H3" s="44"/>
+      <c r="H3" s="61"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
     </row>
     <row r="4" spans="1:43" ht="31.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="40" t="s">
+      <c r="A4" s="57" t="s">
         <v>24</v>
       </c>
-      <c r="B4" s="41"/>
-      <c r="C4" s="41"/>
-      <c r="D4" s="41"/>
-      <c r="E4" s="42"/>
+      <c r="B4" s="58"/>
+      <c r="C4" s="58"/>
+      <c r="D4" s="58"/>
+      <c r="E4" s="59"/>
       <c r="F4" s="14" t="s">
         <v>4</v>
       </c>
@@ -1295,22 +1295,22 @@
       </c>
     </row>
     <row r="5" spans="1:43" ht="31.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="58" t="s">
-        <v>27</v>
-      </c>
-      <c r="B5" s="59"/>
-      <c r="C5" s="59"/>
-      <c r="D5" s="59"/>
-      <c r="E5" s="59"/>
-      <c r="F5" s="59"/>
-      <c r="G5" s="59"/>
-      <c r="H5" s="60"/>
+      <c r="A5" s="51" t="s">
+        <v>57</v>
+      </c>
+      <c r="B5" s="52"/>
+      <c r="C5" s="52"/>
+      <c r="D5" s="52"/>
+      <c r="E5" s="52"/>
+      <c r="F5" s="52"/>
+      <c r="G5" s="52"/>
+      <c r="H5" s="53"/>
     </row>
     <row r="6" spans="1:43" ht="72" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="45" t="s">
+      <c r="A6" s="37" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="56" t="s">
+      <c r="B6" s="49" t="s">
         <v>6</v>
       </c>
       <c r="C6" s="6" t="s">
@@ -1333,8 +1333,8 @@
       </c>
     </row>
     <row r="7" spans="1:43" s="2" customFormat="1" ht="259.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="46"/>
-      <c r="B7" s="57"/>
+      <c r="A7" s="38"/>
+      <c r="B7" s="50"/>
       <c r="C7" s="8" t="s">
         <v>13</v>
       </c>
@@ -1390,16 +1390,16 @@
       <c r="AQ7"/>
     </row>
     <row r="8" spans="1:43" s="2" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.25">
-      <c r="A8" s="47" t="s">
+      <c r="A8" s="40" t="s">
         <v>19</v>
       </c>
-      <c r="B8" s="48"/>
-      <c r="C8" s="48"/>
-      <c r="D8" s="48"/>
-      <c r="E8" s="48"/>
-      <c r="F8" s="48"/>
-      <c r="G8" s="48"/>
-      <c r="H8" s="49"/>
+      <c r="B8" s="41"/>
+      <c r="C8" s="41"/>
+      <c r="D8" s="41"/>
+      <c r="E8" s="41"/>
+      <c r="F8" s="41"/>
+      <c r="G8" s="41"/>
+      <c r="H8" s="42"/>
       <c r="I8"/>
       <c r="J8"/>
       <c r="K8"/>
@@ -1438,24 +1438,24 @@
     </row>
     <row r="9" spans="1:43" s="2" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="B9" s="25" t="s">
         <v>28</v>
       </c>
-      <c r="B9" s="25" t="s">
-        <v>29</v>
-      </c>
       <c r="C9" s="22" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D9" s="22" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E9" s="26"/>
       <c r="F9" s="26"/>
       <c r="G9" s="22" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H9" s="22" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I9"/>
       <c r="J9"/>
@@ -1495,24 +1495,24 @@
     </row>
     <row r="10" spans="1:43" s="2" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="B10" s="25" t="s">
         <v>31</v>
-      </c>
-      <c r="B10" s="25" t="s">
-        <v>32</v>
       </c>
       <c r="C10" s="26"/>
       <c r="D10" s="26"/>
       <c r="E10" s="22" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F10" s="22" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G10" s="22" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H10" s="22" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I10"/>
       <c r="J10"/>
@@ -1552,24 +1552,24 @@
     </row>
     <row r="11" spans="1:43" s="2" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="B11" s="25" t="s">
         <v>33</v>
-      </c>
-      <c r="B11" s="25" t="s">
-        <v>34</v>
       </c>
       <c r="C11" s="26"/>
       <c r="D11" s="26"/>
       <c r="E11" s="22" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F11" s="22" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G11" s="22" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H11" s="22" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I11"/>
       <c r="J11"/>
@@ -1609,26 +1609,26 @@
     </row>
     <row r="12" spans="1:43" s="2" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="B12" s="25" t="s">
         <v>35</v>
       </c>
-      <c r="B12" s="25" t="s">
-        <v>36</v>
-      </c>
       <c r="C12" s="22" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D12" s="22" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E12" s="26"/>
       <c r="F12" s="22" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G12" s="22" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H12" s="22" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I12"/>
       <c r="J12"/>
@@ -1668,24 +1668,24 @@
     </row>
     <row r="13" spans="1:43" s="2" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="B13" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="B13" s="25" t="s">
-        <v>38</v>
-      </c>
       <c r="C13" s="22" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D13" s="22" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E13" s="26"/>
       <c r="F13" s="26"/>
       <c r="G13" s="22" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H13" s="22" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I13"/>
       <c r="J13"/>
@@ -1725,24 +1725,24 @@
     </row>
     <row r="14" spans="1:43" s="2" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="B14" s="25" t="s">
         <v>39</v>
       </c>
-      <c r="B14" s="25" t="s">
-        <v>40</v>
-      </c>
       <c r="C14" s="22" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D14" s="22" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E14" s="26"/>
       <c r="F14" s="26"/>
       <c r="G14" s="22" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H14" s="22" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I14"/>
       <c r="J14"/>
@@ -1782,24 +1782,24 @@
     </row>
     <row r="15" spans="1:43" s="2" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="B15" s="25" t="s">
         <v>41</v>
       </c>
-      <c r="B15" s="25" t="s">
-        <v>42</v>
-      </c>
       <c r="C15" s="22" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D15" s="22" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E15" s="26"/>
       <c r="F15" s="26"/>
       <c r="G15" s="22" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H15" s="22" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I15"/>
       <c r="J15"/>
@@ -1839,22 +1839,22 @@
     </row>
     <row r="16" spans="1:43" s="2" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="B16" s="25" t="s">
         <v>43</v>
       </c>
-      <c r="B16" s="25" t="s">
-        <v>44</v>
-      </c>
       <c r="C16" s="22" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D16" s="26"/>
       <c r="E16" s="26"/>
       <c r="F16" s="26"/>
       <c r="G16" s="22" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H16" s="22" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I16"/>
       <c r="J16"/>
@@ -1894,26 +1894,26 @@
     </row>
     <row r="17" spans="1:43" s="2" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="B17" s="25" t="s">
         <v>45</v>
       </c>
-      <c r="B17" s="25" t="s">
-        <v>46</v>
-      </c>
       <c r="C17" s="22" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D17" s="22" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E17" s="26"/>
       <c r="F17" s="22" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G17" s="22" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H17" s="22" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I17"/>
       <c r="J17"/>
@@ -1953,26 +1953,26 @@
     </row>
     <row r="18" spans="1:43" s="2" customFormat="1" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="27" t="s">
+        <v>46</v>
+      </c>
+      <c r="B18" s="28" t="s">
         <v>47</v>
       </c>
-      <c r="B18" s="28" t="s">
-        <v>48</v>
-      </c>
       <c r="C18" s="29" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D18" s="29" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E18" s="30"/>
       <c r="F18" s="29" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G18" s="29" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H18" s="29" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I18"/>
       <c r="J18"/>
@@ -2011,16 +2011,16 @@
       <c r="AQ18"/>
     </row>
     <row r="19" spans="1:43" s="2" customFormat="1" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="50" t="s">
+      <c r="A19" s="43" t="s">
         <v>20</v>
       </c>
-      <c r="B19" s="51"/>
-      <c r="C19" s="51"/>
-      <c r="D19" s="51"/>
-      <c r="E19" s="51"/>
-      <c r="F19" s="51"/>
-      <c r="G19" s="51"/>
-      <c r="H19" s="52"/>
+      <c r="B19" s="44"/>
+      <c r="C19" s="44"/>
+      <c r="D19" s="44"/>
+      <c r="E19" s="44"/>
+      <c r="F19" s="44"/>
+      <c r="G19" s="44"/>
+      <c r="H19" s="45"/>
       <c r="I19"/>
       <c r="J19"/>
       <c r="K19"/>
@@ -2059,21 +2059,21 @@
     </row>
     <row r="20" spans="1:43" s="2" customFormat="1" ht="46.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="31" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B20" s="32" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C20" s="33" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D20" s="34" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E20" s="34"/>
       <c r="F20" s="34"/>
       <c r="G20" s="34" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H20" s="35"/>
       <c r="I20"/>
@@ -2114,23 +2114,23 @@
     </row>
     <row r="21" spans="1:43" s="2" customFormat="1" ht="46.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="21" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B21" s="24" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C21" s="22" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D21" s="22" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E21" s="22"/>
       <c r="F21" s="22" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G21" s="22" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H21" s="23"/>
       <c r="I21"/>
@@ -2171,21 +2171,21 @@
     </row>
     <row r="22" spans="1:43" s="2" customFormat="1" ht="46.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="21" t="s">
-        <v>51</v>
-      </c>
-      <c r="B22" s="61">
+        <v>50</v>
+      </c>
+      <c r="B22" s="36">
         <v>46183</v>
       </c>
       <c r="C22" s="22" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D22" s="22" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E22" s="22"/>
       <c r="F22" s="22"/>
       <c r="G22" s="22" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H22" s="23"/>
       <c r="I22"/>
@@ -2226,23 +2226,23 @@
     </row>
     <row r="23" spans="1:43" s="2" customFormat="1" ht="46.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="21" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B23" s="24" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C23" s="22" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D23" s="22" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E23" s="22"/>
       <c r="F23" s="22" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G23" s="22" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H23" s="23"/>
       <c r="I23"/>
@@ -2283,21 +2283,21 @@
     </row>
     <row r="24" spans="1:43" s="2" customFormat="1" ht="46.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="21" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B24" s="24" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C24" s="22" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D24" s="22" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E24" s="22"/>
       <c r="F24" s="22"/>
       <c r="G24" s="22" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H24" s="23"/>
       <c r="I24"/>
@@ -2427,16 +2427,16 @@
       <c r="AQ26"/>
     </row>
     <row r="27" spans="1:43" s="2" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.25">
-      <c r="A27" s="53" t="s">
+      <c r="A27" s="46" t="s">
         <v>21</v>
       </c>
-      <c r="B27" s="54"/>
-      <c r="C27" s="54"/>
-      <c r="D27" s="54"/>
-      <c r="E27" s="54"/>
-      <c r="F27" s="54"/>
-      <c r="G27" s="54"/>
-      <c r="H27" s="55"/>
+      <c r="B27" s="47"/>
+      <c r="C27" s="47"/>
+      <c r="D27" s="47"/>
+      <c r="E27" s="47"/>
+      <c r="F27" s="47"/>
+      <c r="G27" s="47"/>
+      <c r="H27" s="48"/>
       <c r="I27"/>
       <c r="J27"/>
       <c r="K27"/>
@@ -2835,6 +2835,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="F3:H3"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A8:H8"/>
@@ -2842,11 +2847,6 @@
     <mergeCell ref="A27:H27"/>
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="A5:H5"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="F3:H3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
